--- a/monitoring_forms/034_ocd_monitoring_form--monitoring_forms.xlsx
+++ b/monitoring_forms/034_ocd_monitoring_form--monitoring_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -600,14 +600,14 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -623,14 +623,14 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,30 +646,30 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>patient_feedback</t>
+          <t>follow_up_schedule</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Patient Feedback</t>
+          <t>Follow-up Schedule</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>patient_feedback</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Patient Feedback</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,113 +699,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>monitoring_frequency_2</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Monitoring Frequency</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ocd_qol_2</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>OCQOL</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>treatment_effectiveness_2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Treatment Effectiveness</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>patient_feedback_2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Patient Feedback</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>additional_comments_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Additional Comments</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -822,12 +730,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>medication_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Medication A</t>
         </is>
       </c>
     </row>
@@ -872,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>medication_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Medication B</t>
         </is>
       </c>
     </row>
@@ -889,216 +797,63 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>medication_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>Medication C</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ocd_qol_choices</t>
+          <t>treatment_effectiveness_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>very_effective</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Very effective</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ocd_qol_choices</t>
+          <t>treatment_effectiveness_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>somewhat_effective</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Somewhat effective</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ocd_qol_choices</t>
+          <t>treatment_effectiveness_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>not_effective</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Item 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>treatment_effectiveness_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>item_1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Item 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>treatment_effectiveness_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>item_2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Item 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>treatment_effectiveness_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>item_3</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Item 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ocd_qol_2_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>item_1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Item 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ocd_qol_2_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>item_2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Item 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ocd_qol_2_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>item_3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Item 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>treatment_effectiveness_2_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>item_1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Item 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>treatment_effectiveness_2_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>item_2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Item 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>treatment_effectiveness_2_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>item_3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Item 3</t>
+          <t>Not effective</t>
         </is>
       </c>
     </row>
